--- a/alumni_data.xlsx
+++ b/alumni_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karaz\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveswinburneeduau-my.sharepoint.com/personal/bzaferanloo_swin_edu_au/Documents/Website - Shaping STEM Futures/S2 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBAF5A6-E8ED-4548-9042-712ECFDC64FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{69E1DE2F-21AD-4C55-96FA-F4FA32A632BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="177">
   <si>
     <t>Full Name</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Matthew Schipper</t>
   </si>
   <si>
-    <t>Jordan Rae</t>
+    <t>Jordan Rai</t>
   </si>
   <si>
     <t>Khanh Vu</t>
@@ -163,12 +163,45 @@
     <t>Emily Cheng</t>
   </si>
   <si>
+    <t>Matthew Clark</t>
+  </si>
+  <si>
+    <t>Yasmin Crestani</t>
+  </si>
+  <si>
+    <t>Katiana Huet-Murphy</t>
+  </si>
+  <si>
+    <t>Wishaya Jansma-Smith</t>
+  </si>
+  <si>
+    <t>Moochie Jarvis</t>
+  </si>
+  <si>
+    <t>Maymuna Kalif</t>
+  </si>
+  <si>
+    <t>Charley Kitto</t>
+  </si>
+  <si>
+    <t>Isabelle Muhlberg</t>
+  </si>
+  <si>
+    <t>Ruby Price</t>
+  </si>
+  <si>
+    <t>Chloe Thompson</t>
+  </si>
+  <si>
     <t>Start Talking</t>
   </si>
   <si>
     <t>Design for Change</t>
   </si>
   <si>
+    <t>Climate Change Study Tour</t>
+  </si>
+  <si>
     <t>Magic Moss: When Walls Come Alive</t>
   </si>
   <si>
@@ -229,13 +262,178 @@
     <t>SisterCloud</t>
   </si>
   <si>
+    <t>Climate Change in Malaysia Study Tour 2024</t>
+  </si>
+  <si>
+    <t>Climate Change in Malaysia Study Tour 2024 (Withdrawn)</t>
+  </si>
+  <si>
     <t>Environmental Science</t>
   </si>
   <si>
+    <t xml:space="preserve">Biotechnology </t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Master of Information Technology</t>
+    <t>Biotechnology and Chemistry</t>
+  </si>
+  <si>
+    <t>Statistical Genetics</t>
+  </si>
+  <si>
+    <t>Health Science</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Philosophy in Photovoltaic Engineering</t>
+  </si>
+  <si>
+    <t>Information Technology in Data Analytics</t>
+  </si>
+  <si>
+    <t>Software Engineering</t>
+  </si>
+  <si>
+    <t>Robotics and Mechatronics</t>
+  </si>
+  <si>
+    <t>Mehatronics, Robotics and Automation Engineering</t>
+  </si>
+  <si>
+    <t>Computer Science</t>
+  </si>
+  <si>
+    <t>Computer Science &amp; Network Design</t>
+  </si>
+  <si>
+    <t>Computer Science, Software Design</t>
+  </si>
+  <si>
+    <t>Engineering Education</t>
+  </si>
+  <si>
+    <t>Software Development, Cloud Computing</t>
+  </si>
+  <si>
+    <t>Master of IT</t>
+  </si>
+  <si>
+    <t>Climate and Social Justice</t>
+  </si>
+  <si>
+    <t>Criminology, Politics &amp; International Relations</t>
+  </si>
+  <si>
+    <t>Bachelor of Laws (LLB)</t>
+  </si>
+  <si>
+    <t>N/A (Withdrawn)</t>
+  </si>
+  <si>
+    <t>N/A (No Degree Listed)</t>
+  </si>
+  <si>
+    <t>Biotechnology and Environmental Science</t>
+  </si>
+  <si>
+    <t>Analytical Chemist[Sarawak Biodiversity Centre, Jan2026]</t>
+  </si>
+  <si>
+    <t>Clinical Data Analyst[Parexel International]</t>
+  </si>
+  <si>
+    <t>Research Assistant[Cancer Research Malaysia]</t>
+  </si>
+  <si>
+    <t>Senior IT Support Officer[Johns Lying Group]</t>
+  </si>
+  <si>
+    <t>Tutor[WEHI]</t>
+  </si>
+  <si>
+    <t>Research Laboratory Manager[ Peter MacCallum Cancer Centre]</t>
+  </si>
+  <si>
+    <t>Laboratory intern[ BORNEO medical centre, Aug2026]</t>
+  </si>
+  <si>
+    <t>Environmental Intern[Chemsain Kolsantant Sdn Bhd, Mar2026]</t>
+  </si>
+  <si>
+    <t>EPX Testing Engineer[ANCA CNC Machines, Jan2025]</t>
+  </si>
+  <si>
+    <t>Executive[Solarvest]</t>
+  </si>
+  <si>
+    <t>Research Study Assistant[University of Melbourne]</t>
+  </si>
+  <si>
+    <t>Account Manager</t>
+  </si>
+  <si>
+    <t>AI Workflow Automation Software Developer</t>
+  </si>
+  <si>
+    <t>IT Consultant[Spine and Orthopaedic Centre]</t>
+  </si>
+  <si>
+    <t>iOS Software Engineer[News Corp Australia]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employability Peer Asistant </t>
+  </si>
+  <si>
+    <t>Voaction Student[Infrabuild]</t>
+  </si>
+  <si>
+    <t>Lead FullStack Engineer[Netrevenue, Jun2026]</t>
+  </si>
+  <si>
+    <t>Software Quality and Assurance Developer[Aglient Technologies]</t>
+  </si>
+  <si>
+    <t>Software Engineer Internship[One Australia Education Group, Nov2024]</t>
+  </si>
+  <si>
+    <t>Software Engineer[BAE Systems Australia]</t>
+  </si>
+  <si>
+    <t>Assosiate Dean</t>
+  </si>
+  <si>
+    <t>Technical Consultant</t>
+  </si>
+  <si>
+    <t>Helpdesk Officer[St. Mary Anglican Girls School]</t>
+  </si>
+  <si>
+    <t>Software Engineer[Thales]</t>
+  </si>
+  <si>
+    <t>N/A (No Position Listed)</t>
+  </si>
+  <si>
+    <t>House Supervisor[Berry Street]</t>
+  </si>
+  <si>
+    <t>Business Development Executive[Odoo, Feb2025]</t>
+  </si>
+  <si>
+    <t>Business Administrative Officer[Yarra Ranges Council]</t>
+  </si>
+  <si>
+    <t>Trainee Scientist[St Vincent's Health Australia]</t>
+  </si>
+  <si>
+    <t>Industrial Placement Student[CSIRO Internship, Jan2024]</t>
   </si>
   <si>
     <t>https://www.linkedin.com/in/hui-ting-yap-074801383/</t>
@@ -250,6 +448,9 @@
     <t>https://www.linkedin.com/in/stephaniecheahhaoling/</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/jordan-rai-56a6971b3/</t>
+  </si>
+  <si>
     <t>https://www.linkedin.com/in/nhan-khanh-vu/</t>
   </si>
   <si>
@@ -265,6 +466,9 @@
     <t>https://www.linkedin.com/in/celine-amelia-d-5b1322328/</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/siti-nurmaisarah-044621328/</t>
+  </si>
+  <si>
     <t>https://www.linkedin.com/in/bahja-abdellatif-35a213304/</t>
   </si>
   <si>
@@ -274,6 +478,9 @@
     <t>https://www.linkedin.com/in/celestina-j-7055a1201/</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/georgie-aiuto-06a7211b1/</t>
+  </si>
+  <si>
     <t>https://www.linkedin.com/in/indradi-lukman/</t>
   </si>
   <si>
@@ -295,9 +502,15 @@
     <t>https://www.linkedin.com/in/erfan-m-b618b3162/</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/nicholas-j-french/</t>
+  </si>
+  <si>
     <t>https://www.linkedin.com/in/alexander-morris-318549186/</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/trung-quoc-doan/</t>
+  </si>
+  <si>
     <t>https://www.linkedin.com/in/jackson-semmens/</t>
   </si>
   <si>
@@ -307,110 +520,44 @@
     <t>https://www.linkedin.com/in/mbejan/</t>
   </si>
   <si>
-    <t>Clinical Data Analyst[Parexel International]</t>
-  </si>
-  <si>
-    <t>Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biotechnology </t>
-  </si>
-  <si>
-    <t>Research Assistant[Cancer Research Malaysia]</t>
-  </si>
-  <si>
-    <t>Statistical Genetics</t>
-  </si>
-  <si>
-    <t>Tutor[WEHI]</t>
-  </si>
-  <si>
-    <t>Biotechnology and Chemistry</t>
-  </si>
-  <si>
-    <t>Research Laboratory Manager[ Peter MacCallum Cancer Centre]</t>
-  </si>
-  <si>
-    <t>Health Science</t>
-  </si>
-  <si>
-    <t>Biotechnology</t>
-  </si>
-  <si>
-    <t>EPX Testing Engineer[ANCA CNC Machines, Jan2025]</t>
-  </si>
-  <si>
-    <t>Laboratory intern[ BORNEO medical centre, Aug2026]</t>
-  </si>
-  <si>
-    <t>Analytical Chemist[Sarawak Biodiversity Centre, Jan2026]</t>
-  </si>
-  <si>
-    <t>Philosophy in Photovoltaic Engineering</t>
-  </si>
-  <si>
-    <t>Executive[Solarvest]</t>
-  </si>
-  <si>
-    <t>Information Technology in Data Analytics</t>
-  </si>
-  <si>
-    <t>Account Manager</t>
-  </si>
-  <si>
-    <t>AI Workflow Automation Software Developer</t>
-  </si>
-  <si>
-    <t>Software Engineering</t>
-  </si>
-  <si>
-    <t>IT Consultant[Spine and Orthopaedic Centre]</t>
-  </si>
-  <si>
-    <t>iOS Software Engineer[News Corp Australia]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employability Peer Asistant </t>
-  </si>
-  <si>
-    <t>Robotics and Mechatronics</t>
-  </si>
-  <si>
-    <t>Voaction Student[Infrabuild]</t>
-  </si>
-  <si>
-    <t>Mehatronics, Robotics and Automation Engineering</t>
-  </si>
-  <si>
-    <t>Software Quality and Assurance Developer[Aglient Technologies]</t>
-  </si>
-  <si>
-    <t>Computer Science &amp; Network Design</t>
-  </si>
-  <si>
-    <t>Software Engineer[BAE Systems Australia]</t>
-  </si>
-  <si>
-    <t>Computer Science, Software Design</t>
-  </si>
-  <si>
-    <t>Assosiate Dean</t>
-  </si>
-  <si>
-    <t>Engineering Education</t>
-  </si>
-  <si>
-    <t>Technical Consultant</t>
-  </si>
-  <si>
-    <t>Software Development, Cloud Computing</t>
+    <t>https://www.linkedin.com/in/shan196/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/emilycheng16/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/yasmin-crestani-430695208/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/katiana-huet-murphy-19741921b/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/wishaya-la-spina-64076b22a/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/maymuna-kalif-06010a3ba/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/charleyk/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ruby-price-736743316/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/chloe-thompson-330052241/</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>Science in Physics</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -430,11 +577,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -478,16 +620,12 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -793,15 +931,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="55.08984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="44.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="55.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="61.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="58" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -833,22 +971,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C2">
         <v>2025</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="F2" t="s">
         <v>107</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>72</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -856,22 +994,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C3">
         <v>2024</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="F3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>73</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -879,22 +1017,19 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C4">
         <v>2023</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F4" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -902,22 +1037,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>2022</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>75</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -925,22 +1060,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C6">
         <v>2021</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -948,22 +1083,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>2020</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" t="s">
-        <v>70</v>
+        <v>110</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -971,45 +1106,45 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C8">
         <v>2025</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>2025</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>102</v>
+        <v>86</v>
+      </c>
+      <c r="F9" t="s">
+        <v>112</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -1017,22 +1152,19 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C10">
         <v>2025</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -1040,22 +1172,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C11">
         <v>2025</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -1063,22 +1195,19 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C12">
         <v>2024</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>104</v>
-      </c>
-      <c r="F12" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1086,22 +1215,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C13">
         <v>2024</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F13" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>80</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -1109,22 +1238,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C14">
         <v>2024</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1132,22 +1261,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C15">
         <v>2024</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
-      </c>
-      <c r="G15" t="s">
-        <v>70</v>
+        <v>114</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -1155,22 +1284,19 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C16">
         <v>2023</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
-      </c>
-      <c r="F16" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1178,22 +1304,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C17">
         <v>2022</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="F17" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -1201,22 +1327,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C18">
         <v>2021</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -1224,22 +1350,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C19">
         <v>2020</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="F19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>70</v>
+        <v>117</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1247,22 +1373,19 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C20">
         <v>2026</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s">
-        <v>110</v>
-      </c>
-      <c r="F20" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1270,22 +1393,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C21">
         <v>2026</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>85</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -1293,22 +1416,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C22">
         <v>2026</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G22" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -1316,22 +1439,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C23">
         <v>2026</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -1339,22 +1462,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C24">
         <v>2026</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="F24" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>86</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -1362,22 +1485,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C25">
         <v>2026</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E25" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="F25" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -1385,22 +1508,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C26">
         <v>2025</v>
       </c>
       <c r="D26" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E26" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="F26" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>88</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -1408,22 +1531,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C27">
         <v>2025</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F27" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G27" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -1431,22 +1554,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C28">
         <v>2024</v>
       </c>
       <c r="D28" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E28" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G28" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -1454,22 +1577,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C29">
         <v>2024</v>
       </c>
       <c r="D29" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E29" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F29" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>89</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -1477,22 +1600,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C30">
         <v>2023</v>
       </c>
       <c r="D30" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="F30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -1500,22 +1623,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C31">
         <v>2022</v>
       </c>
       <c r="D31" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F31" t="s">
-        <v>70</v>
-      </c>
-      <c r="G31" t="s">
-        <v>70</v>
+        <v>124</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -1523,22 +1646,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C32">
         <v>2022</v>
       </c>
       <c r="D32" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E32" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="F32" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -1546,22 +1669,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <v>2022</v>
       </c>
       <c r="D33" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E33" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F33" t="s">
-        <v>70</v>
-      </c>
-      <c r="G33" t="s">
-        <v>70</v>
+        <v>126</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -1569,22 +1692,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C34">
         <v>2022</v>
       </c>
       <c r="D34" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E34" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F34" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G34" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -1592,22 +1715,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>2022</v>
       </c>
       <c r="D35" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E35" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="F35" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -1615,22 +1738,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>2021</v>
       </c>
       <c r="D36" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E36" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="F36" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>93</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -1638,22 +1761,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C37">
         <v>2021</v>
       </c>
       <c r="D37" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E37" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G37" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -1661,22 +1784,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C38">
         <v>2021</v>
       </c>
       <c r="D38" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E38" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="F38" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>94</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -1684,22 +1807,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C39">
         <v>2021</v>
       </c>
       <c r="D39" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E39" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F39" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G39" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -1707,22 +1830,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C40">
         <v>2021</v>
       </c>
       <c r="D40" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E40" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
-        <v>70</v>
-      </c>
-      <c r="G40" t="s">
-        <v>70</v>
+        <v>130</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
@@ -1730,22 +1853,252 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C41">
         <v>2021</v>
       </c>
       <c r="D41" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E41" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F41" t="s">
-        <v>70</v>
-      </c>
-      <c r="G41" t="s">
-        <v>70</v>
+        <v>131</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42">
+        <v>2024</v>
+      </c>
+      <c r="D42" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" t="s">
+        <v>85</v>
+      </c>
+      <c r="G42" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43">
+        <v>2024</v>
+      </c>
+      <c r="D43" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" t="s">
+        <v>132</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44">
+        <v>2024</v>
+      </c>
+      <c r="D44" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" t="s">
+        <v>133</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45">
+        <v>2024</v>
+      </c>
+      <c r="D45" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" t="s">
+        <v>103</v>
+      </c>
+      <c r="F45" t="s">
+        <v>134</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46">
+        <v>2024</v>
+      </c>
+      <c r="D46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E46" t="s">
+        <v>85</v>
+      </c>
+      <c r="F46" t="s">
+        <v>85</v>
+      </c>
+      <c r="G46" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47">
+        <v>2024</v>
+      </c>
+      <c r="D47" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" t="s">
+        <v>104</v>
+      </c>
+      <c r="F47" t="s">
+        <v>132</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48">
+        <v>2024</v>
+      </c>
+      <c r="D48" t="s">
+        <v>80</v>
+      </c>
+      <c r="E48" t="s">
+        <v>103</v>
+      </c>
+      <c r="F48" t="s">
+        <v>135</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49">
+        <v>2024</v>
+      </c>
+      <c r="D49" t="s">
+        <v>80</v>
+      </c>
+      <c r="E49" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" t="s">
+        <v>85</v>
+      </c>
+      <c r="G49" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50">
+        <v>2024</v>
+      </c>
+      <c r="D50" t="s">
+        <v>80</v>
+      </c>
+      <c r="E50" t="s">
+        <v>105</v>
+      </c>
+      <c r="F50" t="s">
+        <v>136</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51">
+        <v>2024</v>
+      </c>
+      <c r="D51" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" t="s">
+        <v>106</v>
+      </c>
+      <c r="F51" t="s">
+        <v>137</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -1754,26 +2107,39 @@
     <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="G8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="G9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="G10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="G12" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="G13" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="G16" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="G17" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="G18" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="G19" r:id="rId13" display="https://www.linkedin.com/in/georgina-dimopoulos-gd/" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="G20" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="G21" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="G24" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="G25" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="G26" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="G29" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="G30" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="G32" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="G35" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="G36" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="G38" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="G7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="G8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="G9" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="G10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="G12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="G13" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="G15" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="G16" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="G17" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="G18" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="G19" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="G20" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="G21" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="G24" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="G25" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="G26" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="G29" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="G30" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="G31" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="G32" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="G33" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="G35" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="G36" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="G38" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="G40" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="G41" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="G43" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="G44" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="G45" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="G47" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="G48" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="G50" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="G51" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/alumni_data.xlsx
+++ b/alumni_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveswinburneeduau-my.sharepoint.com/personal/bzaferanloo_swin_edu_au/Documents/Website - Shaping STEM Futures/S2 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d79e2c508e5e5314/Desktop/Documents/GitHub/alumni_dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69E1DE2F-21AD-4C55-96FA-F4FA32A632BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{69E1DE2F-21AD-4C55-96FA-F4FA32A632BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F61D260-D377-4881-95F4-61403379C68E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,9 +292,6 @@
     <t>Biotechnology</t>
   </si>
   <si>
-    <t>Philosophy in Photovoltaic Engineering</t>
-  </si>
-  <si>
     <t>Information Technology in Data Analytics</t>
   </si>
   <si>
@@ -551,6 +548,9 @@
   </si>
   <si>
     <t>Science in Physics</t>
+  </si>
+  <si>
+    <t>PhD Photovoltaic Engineering</t>
   </si>
 </sst>
 </file>
@@ -983,10 +983,10 @@
         <v>82</v>
       </c>
       <c r="F2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -1006,10 +1006,10 @@
         <v>83</v>
       </c>
       <c r="F3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -1029,7 +1029,7 @@
         <v>84</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1049,10 +1049,10 @@
         <v>83</v>
       </c>
       <c r="F5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -1095,10 +1095,10 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -1118,10 +1118,10 @@
         <v>87</v>
       </c>
       <c r="F8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -1141,10 +1141,10 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -1164,7 +1164,7 @@
         <v>88</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -1207,7 +1207,7 @@
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1227,10 +1227,10 @@
         <v>89</v>
       </c>
       <c r="F13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -1273,10 +1273,10 @@
         <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -1296,7 +1296,7 @@
         <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1313,13 +1313,13 @@
         <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="F17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -1339,10 +1339,10 @@
         <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -1359,13 +1359,13 @@
         <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1382,10 +1382,10 @@
         <v>72</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1402,13 +1402,13 @@
         <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -1471,13 +1471,13 @@
         <v>72</v>
       </c>
       <c r="E24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -1494,13 +1494,13 @@
         <v>72</v>
       </c>
       <c r="E25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -1517,13 +1517,13 @@
         <v>73</v>
       </c>
       <c r="E26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -1586,13 +1586,13 @@
         <v>76</v>
       </c>
       <c r="E29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -1609,13 +1609,13 @@
         <v>77</v>
       </c>
       <c r="E30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -1632,13 +1632,13 @@
         <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -1655,13 +1655,13 @@
         <v>78</v>
       </c>
       <c r="E32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -1678,13 +1678,13 @@
         <v>78</v>
       </c>
       <c r="E33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
@@ -1724,13 +1724,13 @@
         <v>78</v>
       </c>
       <c r="E35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F35" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -1747,13 +1747,13 @@
         <v>79</v>
       </c>
       <c r="E36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -1793,13 +1793,13 @@
         <v>79</v>
       </c>
       <c r="E38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -1839,13 +1839,13 @@
         <v>79</v>
       </c>
       <c r="E40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F40" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
@@ -1862,13 +1862,13 @@
         <v>79</v>
       </c>
       <c r="E41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
@@ -1908,13 +1908,13 @@
         <v>80</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
@@ -1931,13 +1931,13 @@
         <v>80</v>
       </c>
       <c r="E44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
@@ -1954,13 +1954,13 @@
         <v>80</v>
       </c>
       <c r="E45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F45" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
@@ -2000,13 +2000,13 @@
         <v>81</v>
       </c>
       <c r="E47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F47" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
@@ -2023,13 +2023,13 @@
         <v>80</v>
       </c>
       <c r="E48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F48" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -2069,13 +2069,13 @@
         <v>80</v>
       </c>
       <c r="E50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -2092,13 +2092,13 @@
         <v>80</v>
       </c>
       <c r="E51" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F51" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/alumni_data.xlsx
+++ b/alumni_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d79e2c508e5e5314/Desktop/Documents/GitHub/alumni_dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karaz\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{69E1DE2F-21AD-4C55-96FA-F4FA32A632BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F61D260-D377-4881-95F4-61403379C68E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F219A65A-5415-44F6-8FD7-A8F90C8FBD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="225">
   <si>
     <t>Full Name</t>
   </si>
@@ -37,7 +37,19 @@
     <t>Academic Field Enrolled In</t>
   </si>
   <si>
-    <t xml:space="preserve">Current Position </t>
+    <t>Job Title</t>
+  </si>
+  <si>
+    <t>Employer</t>
+  </si>
+  <si>
+    <t>Placement</t>
+  </si>
+  <si>
+    <t>Placement Organization</t>
+  </si>
+  <si>
+    <t>Further Study</t>
   </si>
   <si>
     <t>LinkedIn Profile</t>
@@ -277,160 +289,223 @@
     <t>Science</t>
   </si>
   <si>
+    <t>Biotechnology and Chemistry</t>
+  </si>
+  <si>
+    <t>Statistical Genetics</t>
+  </si>
+  <si>
+    <t>Health Science</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Philosophy in Photovoltaic Engineering</t>
+  </si>
+  <si>
+    <t>Bachelor of Science, Physics</t>
+  </si>
+  <si>
+    <t>Information Technology in Data Analytics</t>
+  </si>
+  <si>
+    <t>Software Engineering</t>
+  </si>
+  <si>
+    <t>Master of Information Technology</t>
+  </si>
+  <si>
+    <t>Robotics and Mechatronics</t>
+  </si>
+  <si>
+    <t>Mehatronics, Robotics and Automation Engineering</t>
+  </si>
+  <si>
+    <t>Computer Science</t>
+  </si>
+  <si>
+    <t>Computer Science &amp; Network Design</t>
+  </si>
+  <si>
+    <t>Computer Science, Software Design</t>
+  </si>
+  <si>
+    <t>Engineering Education</t>
+  </si>
+  <si>
+    <t>Software Development, Cloud Computing</t>
+  </si>
+  <si>
+    <t>Master of IT</t>
+  </si>
+  <si>
+    <t>Climate and Social Justice</t>
+  </si>
+  <si>
+    <t>Criminology, Politics &amp; International Relations</t>
+  </si>
+  <si>
+    <t>Bachelor of Laws (LLB)</t>
+  </si>
+  <si>
+    <t>N/A (Withdrawn)</t>
+  </si>
+  <si>
+    <t>N/A (No Degree Listed)</t>
+  </si>
+  <si>
+    <t>Biotechnology and Environmental Science</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Biotechnology and Chemistry</t>
-  </si>
-  <si>
-    <t>Statistical Genetics</t>
-  </si>
-  <si>
-    <t>Health Science</t>
-  </si>
-  <si>
-    <t>Biotechnology</t>
-  </si>
-  <si>
-    <t>Information Technology in Data Analytics</t>
-  </si>
-  <si>
-    <t>Software Engineering</t>
-  </si>
-  <si>
-    <t>Robotics and Mechatronics</t>
-  </si>
-  <si>
-    <t>Mehatronics, Robotics and Automation Engineering</t>
-  </si>
-  <si>
-    <t>Computer Science</t>
-  </si>
-  <si>
-    <t>Computer Science &amp; Network Design</t>
-  </si>
-  <si>
-    <t>Computer Science, Software Design</t>
-  </si>
-  <si>
-    <t>Engineering Education</t>
-  </si>
-  <si>
-    <t>Software Development, Cloud Computing</t>
-  </si>
-  <si>
-    <t>Master of IT</t>
-  </si>
-  <si>
-    <t>Climate and Social Justice</t>
-  </si>
-  <si>
-    <t>Criminology, Politics &amp; International Relations</t>
-  </si>
-  <si>
-    <t>Bachelor of Laws (LLB)</t>
-  </si>
-  <si>
-    <t>N/A (Withdrawn)</t>
-  </si>
-  <si>
-    <t>N/A (No Degree Listed)</t>
-  </si>
-  <si>
-    <t>Biotechnology and Environmental Science</t>
-  </si>
-  <si>
-    <t>Analytical Chemist[Sarawak Biodiversity Centre, Jan2026]</t>
-  </si>
-  <si>
-    <t>Clinical Data Analyst[Parexel International]</t>
-  </si>
-  <si>
-    <t>Research Assistant[Cancer Research Malaysia]</t>
-  </si>
-  <si>
-    <t>Senior IT Support Officer[Johns Lying Group]</t>
-  </si>
-  <si>
-    <t>Tutor[WEHI]</t>
-  </si>
-  <si>
-    <t>Research Laboratory Manager[ Peter MacCallum Cancer Centre]</t>
-  </si>
-  <si>
-    <t>Laboratory intern[ BORNEO medical centre, Aug2026]</t>
-  </si>
-  <si>
-    <t>Environmental Intern[Chemsain Kolsantant Sdn Bhd, Mar2026]</t>
-  </si>
-  <si>
-    <t>EPX Testing Engineer[ANCA CNC Machines, Jan2025]</t>
-  </si>
-  <si>
-    <t>Executive[Solarvest]</t>
-  </si>
-  <si>
-    <t>Research Study Assistant[University of Melbourne]</t>
-  </si>
-  <si>
     <t>Account Manager</t>
   </si>
   <si>
     <t>AI Workflow Automation Software Developer</t>
   </si>
   <si>
-    <t>IT Consultant[Spine and Orthopaedic Centre]</t>
-  </si>
-  <si>
-    <t>iOS Software Engineer[News Corp Australia]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employability Peer Asistant </t>
-  </si>
-  <si>
-    <t>Voaction Student[Infrabuild]</t>
-  </si>
-  <si>
-    <t>Lead FullStack Engineer[Netrevenue, Jun2026]</t>
-  </si>
-  <si>
-    <t>Software Quality and Assurance Developer[Aglient Technologies]</t>
-  </si>
-  <si>
-    <t>Software Engineer Internship[One Australia Education Group, Nov2024]</t>
-  </si>
-  <si>
-    <t>Software Engineer[BAE Systems Australia]</t>
-  </si>
-  <si>
     <t>Assosiate Dean</t>
   </si>
   <si>
     <t>Technical Consultant</t>
   </si>
   <si>
-    <t>Helpdesk Officer[St. Mary Anglican Girls School]</t>
-  </si>
-  <si>
-    <t>Software Engineer[Thales]</t>
-  </si>
-  <si>
-    <t>N/A (No Position Listed)</t>
-  </si>
-  <si>
-    <t>House Supervisor[Berry Street]</t>
-  </si>
-  <si>
-    <t>Business Development Executive[Odoo, Feb2025]</t>
-  </si>
-  <si>
-    <t>Business Administrative Officer[Yarra Ranges Council]</t>
-  </si>
-  <si>
-    <t>Trainee Scientist[St Vincent's Health Australia]</t>
-  </si>
-  <si>
-    <t>Industrial Placement Student[CSIRO Internship, Jan2024]</t>
+    <t>Clinical Data Analyst</t>
+  </si>
+  <si>
+    <t>Research Assistant</t>
+  </si>
+  <si>
+    <t>Senior IT Support Officer</t>
+  </si>
+  <si>
+    <t>Tutor</t>
+  </si>
+  <si>
+    <t>Research Laboratory Manager</t>
+  </si>
+  <si>
+    <t>Executive</t>
+  </si>
+  <si>
+    <t>Research Study Assistant</t>
+  </si>
+  <si>
+    <t>IT Consultant</t>
+  </si>
+  <si>
+    <t>iOS Software Engineer</t>
+  </si>
+  <si>
+    <t>Employability Peer Asistant</t>
+  </si>
+  <si>
+    <t>Voaction Student</t>
+  </si>
+  <si>
+    <t>Software Quality and Assurance Developer</t>
+  </si>
+  <si>
+    <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>Helpdesk Officer</t>
+  </si>
+  <si>
+    <t>House Supervisor</t>
+  </si>
+  <si>
+    <t>Business Administrative Officer</t>
+  </si>
+  <si>
+    <t>Trainee Scientist</t>
+  </si>
+  <si>
+    <t>Industrial Placement Student</t>
+  </si>
+  <si>
+    <t>Sarawak Biodiversity Centre</t>
+  </si>
+  <si>
+    <t>Parexel International</t>
+  </si>
+  <si>
+    <t>Cancer Research Malaysia</t>
+  </si>
+  <si>
+    <t>Johns Lying Group</t>
+  </si>
+  <si>
+    <t>WEHI</t>
+  </si>
+  <si>
+    <t>Peter MacCallum Cancer Centre</t>
+  </si>
+  <si>
+    <t>BORNEO medical centre</t>
+  </si>
+  <si>
+    <t>Chemsain Kolsantant Sdn Bhd</t>
+  </si>
+  <si>
+    <t>ANCA CNC Machines</t>
+  </si>
+  <si>
+    <t>Solarvest</t>
+  </si>
+  <si>
+    <t>University of Melbourne</t>
+  </si>
+  <si>
+    <t>Self-Employed / Unlisted</t>
+  </si>
+  <si>
+    <t>Spine and Orthopaedic Centre</t>
+  </si>
+  <si>
+    <t>News Corp Australia</t>
+  </si>
+  <si>
+    <t>Infrabuild</t>
+  </si>
+  <si>
+    <t>Netrevenue</t>
+  </si>
+  <si>
+    <t>Aglient Technologies</t>
+  </si>
+  <si>
+    <t>One Australia Education Group</t>
+  </si>
+  <si>
+    <t>BAE Systems Australia</t>
+  </si>
+  <si>
+    <t>St. Mary Anglican Girls School</t>
+  </si>
+  <si>
+    <t>Thales</t>
+  </si>
+  <si>
+    <t>Berry Street</t>
+  </si>
+  <si>
+    <t>Odoo</t>
+  </si>
+  <si>
+    <t>Yarra Ranges Council</t>
+  </si>
+  <si>
+    <t>St Vincent's Health Australia</t>
+  </si>
+  <si>
+    <t>CSIRO Internship</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>https://www.linkedin.com/in/hui-ting-yap-074801383/</t>
@@ -544,13 +619,82 @@
     <t>https://www.linkedin.com/in/chloe-thompson-330052241/</t>
   </si>
   <si>
-    <t>Information Technology</t>
-  </si>
-  <si>
-    <t>Science in Physics</t>
-  </si>
-  <si>
-    <t>PhD Photovoltaic Engineering</t>
+    <t>Analytical Chemist [Jan2026}</t>
+  </si>
+  <si>
+    <t>Laboratory intern[Aug2026]</t>
+  </si>
+  <si>
+    <t>Environmental Intern[Mar2026]</t>
+  </si>
+  <si>
+    <t>EPX Testing Engineer[jan2025]</t>
+  </si>
+  <si>
+    <t>Lead FullStack Engineer[Jun2026]</t>
+  </si>
+  <si>
+    <t>Software Engineer Internship[Nov2024]</t>
+  </si>
+  <si>
+    <t>Business Development Executive[Feb2025]</t>
+  </si>
+  <si>
+    <t>Industrial Placement Student[Jan2024]</t>
+  </si>
+  <si>
+    <t>Laboratory Intern</t>
+  </si>
+  <si>
+    <t>Environment Intern</t>
+  </si>
+  <si>
+    <t>Clinical Data Analyst Intern</t>
+  </si>
+  <si>
+    <t>Graduate Research Assistant</t>
+  </si>
+  <si>
+    <t>DevOps/System Admin</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>AKOOL</t>
+  </si>
+  <si>
+    <t>Komosion</t>
+  </si>
+  <si>
+    <t>Swinburne University of Technology</t>
+  </si>
+  <si>
+    <t>PhD in Statistical Genetics</t>
+  </si>
+  <si>
+    <t>Masters in Photovoltaic Engineering</t>
+  </si>
+  <si>
+    <t>Masters in Education</t>
+  </si>
+  <si>
+    <t>Masters in Infrmation Technology</t>
+  </si>
+  <si>
+    <t>Masters in Information Technology</t>
+  </si>
+  <si>
+    <t>Pearson</t>
+  </si>
+  <si>
+    <t>Application Support Intern</t>
+  </si>
+  <si>
+    <t>SEAM_ARC</t>
+  </si>
+  <si>
+    <t>Research Intern</t>
   </si>
 </sst>
 </file>
@@ -931,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.7265625" bestFit="1" customWidth="1"/>
@@ -939,11 +1083,15 @@
     <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="55.08984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="44.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="61.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="58" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -965,1181 +1113,1730 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C2">
         <v>2025</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+      <c r="G2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" t="s">
+        <v>161</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C3">
         <v>2024</v>
       </c>
       <c r="D3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" t="s">
+        <v>209</v>
+      </c>
+      <c r="I3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J3" t="s">
+        <v>161</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
         <v>61</v>
-      </c>
-      <c r="E3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
       </c>
       <c r="C4">
         <v>2023</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="F4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" t="s">
+        <v>161</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>2022</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+      <c r="G5" t="s">
+        <v>137</v>
+      </c>
+      <c r="H5" t="s">
+        <v>210</v>
+      </c>
+      <c r="I5" t="s">
+        <v>137</v>
+      </c>
+      <c r="J5" t="s">
+        <v>161</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C6">
         <v>2021</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="H6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C7">
         <v>2020</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F7" t="s">
-        <v>109</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+      <c r="G7" t="s">
+        <v>138</v>
+      </c>
+      <c r="H7" t="s">
+        <v>161</v>
+      </c>
+      <c r="I7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C8">
         <v>2025</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F8" t="s">
-        <v>110</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+      <c r="G8" t="s">
+        <v>139</v>
+      </c>
+      <c r="H8" t="s">
+        <v>161</v>
+      </c>
+      <c r="I8" t="s">
+        <v>112</v>
+      </c>
+      <c r="J8" t="s">
+        <v>216</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>2025</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+      <c r="G9" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" t="s">
+        <v>161</v>
+      </c>
+      <c r="I9" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" t="s">
+        <v>161</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C10">
         <v>2025</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+      <c r="F10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H10" t="s">
+        <v>161</v>
+      </c>
+      <c r="I10" t="s">
+        <v>112</v>
+      </c>
+      <c r="J10" t="s">
+        <v>161</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>2025</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="H11" t="s">
+        <v>112</v>
+      </c>
+      <c r="I11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C12">
         <v>2024</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
-        <v>89</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+      <c r="F12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G12" t="s">
+        <v>112</v>
+      </c>
+      <c r="H12" t="s">
+        <v>161</v>
+      </c>
+      <c r="I12" t="s">
+        <v>112</v>
+      </c>
+      <c r="J12" t="s">
+        <v>161</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C13">
         <v>2024</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F13" t="s">
-        <v>112</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+      <c r="G13" t="s">
+        <v>141</v>
+      </c>
+      <c r="H13" t="s">
+        <v>207</v>
+      </c>
+      <c r="I13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J13" t="s">
+        <v>161</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C14">
         <v>2024</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F14" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="H14" t="s">
+        <v>112</v>
+      </c>
+      <c r="I14" t="s">
+        <v>112</v>
+      </c>
+      <c r="J14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C15">
         <v>2024</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F15" t="s">
-        <v>113</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+      <c r="G15" t="s">
+        <v>142</v>
+      </c>
+      <c r="H15" t="s">
+        <v>208</v>
+      </c>
+      <c r="I15" t="s">
+        <v>142</v>
+      </c>
+      <c r="J15" t="s">
+        <v>161</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C16">
         <v>2023</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+      <c r="F16" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" t="s">
+        <v>112</v>
+      </c>
+      <c r="H16" t="s">
+        <v>161</v>
+      </c>
+      <c r="I16" t="s">
+        <v>112</v>
+      </c>
+      <c r="J16" t="s">
+        <v>161</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C17">
         <v>2022</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>176</v>
+        <v>93</v>
       </c>
       <c r="F17" t="s">
-        <v>114</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+      <c r="G17" t="s">
+        <v>143</v>
+      </c>
+      <c r="H17" t="s">
+        <v>224</v>
+      </c>
+      <c r="I17" t="s">
+        <v>223</v>
+      </c>
+      <c r="J17" t="s">
+        <v>217</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C18">
         <v>2021</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+      <c r="G18" t="s">
+        <v>144</v>
+      </c>
+      <c r="H18" t="s">
+        <v>161</v>
+      </c>
+      <c r="I18" t="s">
+        <v>112</v>
+      </c>
+      <c r="J18" t="s">
+        <v>161</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C19">
         <v>2020</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
-        <v>175</v>
+        <v>94</v>
       </c>
       <c r="F19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="G19" t="s">
+        <v>145</v>
+      </c>
+      <c r="H19" t="s">
+        <v>211</v>
+      </c>
+      <c r="I19" t="s">
+        <v>212</v>
+      </c>
+      <c r="J19" t="s">
+        <v>218</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C20">
         <v>2026</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="F20" t="s">
+        <v>112</v>
+      </c>
+      <c r="G20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I20" t="s">
+        <v>112</v>
+      </c>
+      <c r="J20" t="s">
+        <v>161</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C21">
         <v>2026</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s">
-        <v>117</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="G21" t="s">
+        <v>213</v>
+      </c>
+      <c r="H21" t="s">
+        <v>161</v>
+      </c>
+      <c r="I21" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" t="s">
+        <v>161</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C22">
         <v>2026</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F22" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="H22" t="s">
+        <v>112</v>
+      </c>
+      <c r="I22" t="s">
+        <v>112</v>
+      </c>
+      <c r="J22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C23">
         <v>2026</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F23" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="H23" t="s">
+        <v>112</v>
+      </c>
+      <c r="I23" t="s">
+        <v>112</v>
+      </c>
+      <c r="J23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C24">
         <v>2026</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E24" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F24" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="G24" t="s">
+        <v>214</v>
+      </c>
+      <c r="H24" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" t="s">
+        <v>112</v>
+      </c>
+      <c r="J24" t="s">
+        <v>161</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C25">
         <v>2026</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E25" t="s">
-        <v>174</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s">
-        <v>119</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+      <c r="G25" t="s">
+        <v>147</v>
+      </c>
+      <c r="H25" t="s">
+        <v>222</v>
+      </c>
+      <c r="I25" t="s">
+        <v>221</v>
+      </c>
+      <c r="J25" t="s">
+        <v>219</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C26">
         <v>2025</v>
       </c>
       <c r="D26" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E26" t="s">
-        <v>174</v>
+        <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>120</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+      <c r="G26" t="s">
+        <v>148</v>
+      </c>
+      <c r="H26" t="s">
+        <v>161</v>
+      </c>
+      <c r="I26" t="s">
+        <v>112</v>
+      </c>
+      <c r="J26" t="s">
+        <v>220</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C27">
         <v>2025</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G27" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="H27" t="s">
+        <v>112</v>
+      </c>
+      <c r="I27" t="s">
+        <v>112</v>
+      </c>
+      <c r="J27" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C28">
         <v>2024</v>
       </c>
       <c r="D28" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F28" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="H28" t="s">
+        <v>112</v>
+      </c>
+      <c r="I28" t="s">
+        <v>112</v>
+      </c>
+      <c r="J28" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C29">
         <v>2024</v>
       </c>
       <c r="D29" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F29" t="s">
-        <v>121</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+      <c r="G29" t="s">
+        <v>215</v>
+      </c>
+      <c r="H29" t="s">
+        <v>161</v>
+      </c>
+      <c r="I29" t="s">
+        <v>112</v>
+      </c>
+      <c r="J29" t="s">
+        <v>161</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C30">
         <v>2023</v>
       </c>
       <c r="D30" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F30" t="s">
-        <v>122</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+      <c r="G30" t="s">
+        <v>149</v>
+      </c>
+      <c r="H30" t="s">
+        <v>161</v>
+      </c>
+      <c r="I30" t="s">
+        <v>112</v>
+      </c>
+      <c r="J30" t="s">
+        <v>161</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C31">
         <v>2022</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E31" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+        <v>203</v>
+      </c>
+      <c r="G31" t="s">
+        <v>150</v>
+      </c>
+      <c r="H31" t="s">
+        <v>161</v>
+      </c>
+      <c r="I31" t="s">
+        <v>112</v>
+      </c>
+      <c r="J31" t="s">
+        <v>161</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C32">
         <v>2022</v>
       </c>
       <c r="D32" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E32" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F32" t="s">
-        <v>124</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+      <c r="G32" t="s">
+        <v>151</v>
+      </c>
+      <c r="H32" t="s">
+        <v>161</v>
+      </c>
+      <c r="I32" t="s">
+        <v>112</v>
+      </c>
+      <c r="J32" t="s">
+        <v>161</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C33">
         <v>2022</v>
       </c>
       <c r="D33" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E33" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F33" t="s">
-        <v>125</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+      <c r="G33" t="s">
+        <v>152</v>
+      </c>
+      <c r="H33" t="s">
+        <v>129</v>
+      </c>
+      <c r="I33" t="s">
+        <v>152</v>
+      </c>
+      <c r="J33" t="s">
+        <v>161</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C34">
         <v>2022</v>
       </c>
       <c r="D34" t="s">
-        <v>78</v>
-      </c>
-      <c r="E34" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F34" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G34" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="H34" t="s">
+        <v>112</v>
+      </c>
+      <c r="I34" t="s">
+        <v>112</v>
+      </c>
+      <c r="J34" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C35">
         <v>2022</v>
       </c>
       <c r="D35" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E35" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+      <c r="G35" t="s">
+        <v>153</v>
+      </c>
+      <c r="H35" t="s">
+        <v>161</v>
+      </c>
+      <c r="I35" t="s">
+        <v>112</v>
+      </c>
+      <c r="J35" t="s">
+        <v>161</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C36">
         <v>2021</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E36" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F36" t="s">
-        <v>127</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="G36" t="s">
+        <v>215</v>
+      </c>
+      <c r="H36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I36" t="s">
+        <v>112</v>
+      </c>
+      <c r="J36" t="s">
+        <v>161</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C37">
         <v>2021</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
-      </c>
-      <c r="E37" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F37" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G37" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="H37" t="s">
+        <v>112</v>
+      </c>
+      <c r="I37" t="s">
+        <v>112</v>
+      </c>
+      <c r="J37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C38">
         <v>2021</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E38" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F38" t="s">
-        <v>128</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="G38" t="s">
+        <v>146</v>
+      </c>
+      <c r="H38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I38" t="s">
+        <v>112</v>
+      </c>
+      <c r="J38" t="s">
+        <v>161</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>2021</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
-      </c>
-      <c r="E39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F39" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G39" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="H39" t="s">
+        <v>112</v>
+      </c>
+      <c r="I39" t="s">
+        <v>112</v>
+      </c>
+      <c r="J39" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C40">
         <v>2021</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E40" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F40" t="s">
-        <v>129</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+      <c r="G40" t="s">
+        <v>154</v>
+      </c>
+      <c r="H40" t="s">
+        <v>161</v>
+      </c>
+      <c r="I40" t="s">
+        <v>112</v>
+      </c>
+      <c r="J40" t="s">
+        <v>220</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C41">
         <v>2021</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E41" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F41" t="s">
-        <v>130</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+      <c r="G41" t="s">
+        <v>155</v>
+      </c>
+      <c r="H41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I41" t="s">
+        <v>112</v>
+      </c>
+      <c r="J41" t="s">
+        <v>220</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C42">
         <v>2024</v>
       </c>
       <c r="D42" t="s">
-        <v>80</v>
-      </c>
-      <c r="E42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F42" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G42" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="H42" t="s">
+        <v>112</v>
+      </c>
+      <c r="I42" t="s">
+        <v>112</v>
+      </c>
+      <c r="J42" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C43">
         <v>2024</v>
       </c>
       <c r="D43" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E43" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F43" t="s">
-        <v>131</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="G43" t="s">
+        <v>112</v>
+      </c>
+      <c r="H43" t="s">
+        <v>161</v>
+      </c>
+      <c r="I43" t="s">
+        <v>112</v>
+      </c>
+      <c r="J43" t="s">
+        <v>161</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C44">
         <v>2024</v>
       </c>
       <c r="D44" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F44" t="s">
-        <v>132</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+      <c r="G44" t="s">
+        <v>156</v>
+      </c>
+      <c r="H44" t="s">
+        <v>161</v>
+      </c>
+      <c r="I44" t="s">
+        <v>112</v>
+      </c>
+      <c r="J44" t="s">
+        <v>161</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C45">
         <v>2024</v>
       </c>
       <c r="D45" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E45" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F45" t="s">
-        <v>133</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+      <c r="G45" t="s">
+        <v>157</v>
+      </c>
+      <c r="H45" t="s">
+        <v>161</v>
+      </c>
+      <c r="I45" t="s">
+        <v>112</v>
+      </c>
+      <c r="J45" t="s">
+        <v>161</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C46">
         <v>2024</v>
       </c>
       <c r="D46" t="s">
-        <v>80</v>
-      </c>
-      <c r="E46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F46" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G46" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="H46" t="s">
+        <v>112</v>
+      </c>
+      <c r="I46" t="s">
+        <v>112</v>
+      </c>
+      <c r="J46" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C47">
         <v>2024</v>
       </c>
       <c r="D47" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E47" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F47" t="s">
-        <v>131</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="G47" t="s">
+        <v>112</v>
+      </c>
+      <c r="H47" t="s">
+        <v>161</v>
+      </c>
+      <c r="I47" t="s">
+        <v>112</v>
+      </c>
+      <c r="J47" t="s">
+        <v>161</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C48">
         <v>2024</v>
       </c>
       <c r="D48" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E48" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F48" t="s">
-        <v>134</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+      <c r="G48" t="s">
+        <v>158</v>
+      </c>
+      <c r="H48" t="s">
+        <v>161</v>
+      </c>
+      <c r="I48" t="s">
+        <v>112</v>
+      </c>
+      <c r="J48" t="s">
+        <v>161</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C49">
         <v>2024</v>
       </c>
       <c r="D49" t="s">
-        <v>80</v>
-      </c>
-      <c r="E49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F49" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="G49" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+      <c r="H49" t="s">
+        <v>112</v>
+      </c>
+      <c r="I49" t="s">
+        <v>112</v>
+      </c>
+      <c r="J49" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C50">
         <v>2024</v>
       </c>
       <c r="D50" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E50" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F50" t="s">
-        <v>135</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+      <c r="G50" t="s">
+        <v>159</v>
+      </c>
+      <c r="H50" t="s">
+        <v>133</v>
+      </c>
+      <c r="I50" t="s">
+        <v>159</v>
+      </c>
+      <c r="J50" t="s">
+        <v>161</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C51">
         <v>2024</v>
       </c>
       <c r="D51" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E51" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F51" t="s">
-        <v>136</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>173</v>
+        <v>206</v>
+      </c>
+      <c r="G51" t="s">
+        <v>160</v>
+      </c>
+      <c r="H51" t="s">
+        <v>134</v>
+      </c>
+      <c r="I51" t="s">
+        <v>160</v>
+      </c>
+      <c r="J51" t="s">
+        <v>161</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="G7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="G8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="G9" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="G10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="G12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="G13" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="G15" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="G16" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="G17" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="G18" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="G19" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="G20" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="G21" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="G24" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="G25" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="G26" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="G29" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="G30" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="G31" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="G32" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="G33" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="G35" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="G36" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="G38" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="G40" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="G41" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="G43" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="G44" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="G45" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="G47" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="G48" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="G50" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="G51" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="K4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="K5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="K8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="K9" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="K10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="K12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="K13" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="K15" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="K16" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="K17" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="K18" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="K19" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="K20" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="K21" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="K24" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="K25" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="K26" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="K29" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="K30" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="K31" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="K32" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="K33" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="K35" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="K36" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="K38" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="K40" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K41" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="K43" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="K44" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="K45" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="K47" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="K48" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="K50" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="K51" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
